--- a/public/data/monthly-revenue-11506.xlsx
+++ b/public/data/monthly-revenue-11506.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -457,40 +457,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>3580</v>
+        <v>友威科</v>
       </c>
       <c r="B2" t="str">
         <v>友威科</v>
       </c>
       <c r="C2" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>11506</v>
       </c>
       <c r="E2" t="str">
-        <v>43,243</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>44,502</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>-1,259</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>-2.83</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>189,510</v>
+        <v/>
       </c>
       <c r="J2" t="str">
-        <v>203,939</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v>-14,429</v>
+        <v/>
       </c>
       <c r="L2" t="str">
-        <v>-7.08</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -498,40 +498,40 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>3675</v>
+        <v>德微</v>
       </c>
       <c r="B3" t="str">
         <v>德微</v>
       </c>
       <c r="C3" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>11506</v>
       </c>
       <c r="E3" t="str">
-        <v>279,963</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>215,370</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>64,593</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>29.99</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>1,485,502</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>1,268,444</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>217,058</v>
+        <v/>
       </c>
       <c r="L3" t="str">
-        <v>17.11</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -539,163 +539,163 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6414</v>
+        <v>樺漢</v>
       </c>
       <c r="B4" t="str">
         <v>樺漢</v>
       </c>
       <c r="C4" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>11506</v>
       </c>
       <c r="E4" t="str">
-        <v>17,661,254</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>11,251,646</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>6,409,608</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>56.97</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>85,293,283</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>69,158,805</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>16,134,478</v>
+        <v/>
       </c>
       <c r="L4" t="str">
-        <v>23.33</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>AI需求增加、客戶需求強勁</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6416</v>
+        <v>瑞祺電通</v>
       </c>
       <c r="B5" t="str">
         <v>瑞祺電通</v>
       </c>
       <c r="C5" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v>11506</v>
       </c>
       <c r="E5" t="str">
-        <v>667,868</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>421,055</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>246,813</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>58.62</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>2,390,895</v>
+        <v/>
       </c>
       <c r="J5" t="str">
-        <v>2,170,447</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>220,448</v>
+        <v/>
       </c>
       <c r="L5" t="str">
-        <v>10.16</v>
+        <v/>
       </c>
       <c r="M5" t="str">
-        <v>因應上半年部分區域訂單物料遞延，公司於階段性齊料後迅速優化生產排程並加速出貨，帶動6月單月營收成長。</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3305</v>
+        <v>昇貿</v>
       </c>
       <c r="B6" t="str">
         <v>昇貿</v>
       </c>
       <c r="C6" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v>11506</v>
       </c>
       <c r="E6" t="str">
-        <v>1,445,505</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>821,303</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>624,202</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>76.00</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>7,984,628</v>
+        <v/>
       </c>
       <c r="J6" t="str">
-        <v>4,851,602</v>
+        <v/>
       </c>
       <c r="K6" t="str">
-        <v>3,133,026</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>64.58</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>銷售量增加及原料價格上漲</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>8098</v>
+        <v>慶康科技</v>
       </c>
       <c r="B7" t="str">
         <v>慶康科技</v>
       </c>
       <c r="C7" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D7" t="str">
         <v>11506</v>
       </c>
       <c r="E7" t="str">
-        <v>79,912</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>61,161</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>18,751</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>30.66</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>362,103</v>
+        <v/>
       </c>
       <c r="J7" t="str">
-        <v>323,896</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>38,207</v>
+        <v/>
       </c>
       <c r="L7" t="str">
-        <v>11.80</v>
+        <v/>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -703,81 +703,81 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>9958</v>
+        <v>世紀鋼</v>
       </c>
       <c r="B8" t="str">
         <v>世紀鋼</v>
       </c>
       <c r="C8" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D8" t="str">
         <v>11506</v>
       </c>
       <c r="E8" t="str">
-        <v>2,138,665</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>1,303,359</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>835,306</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>64.09</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>10,181,252</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>7,881,335</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v>2,299,917</v>
+        <v/>
       </c>
       <c r="L8" t="str">
-        <v>29.18</v>
+        <v/>
       </c>
       <c r="M8" t="str">
-        <v>本月增加百分比達50%以上，主要係風力事業案依進度如期交貨及相關工程收入挹注所致。</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6672</v>
+        <v>騰輝電子-KY</v>
       </c>
       <c r="B9" t="str">
         <v>騰輝電子-KY</v>
       </c>
       <c r="C9" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D9" t="str">
         <v>11506</v>
       </c>
       <c r="E9" t="str">
-        <v>573,491</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>341,113</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>232,378</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>68.12</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>2,859,714</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>2,125,423</v>
+        <v/>
       </c>
       <c r="K9" t="str">
-        <v>734,291</v>
+        <v/>
       </c>
       <c r="L9" t="str">
-        <v>34.55</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>1560</v>
+        <v>中砂</v>
       </c>
       <c r="B10" t="str">
         <v>中砂</v>
       </c>
       <c r="C10" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D10" t="str">
         <v>11506</v>
       </c>
       <c r="E10" t="str">
-        <v>832,959</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>715,653</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>117,306</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>16.39</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>4,785,855</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v>3,890,219</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>895,636</v>
+        <v/>
       </c>
       <c r="L10" t="str">
-        <v>23.02</v>
+        <v/>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,13 +826,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>3138</v>
+        <v>耀登</v>
       </c>
       <c r="B11" t="str">
         <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v>27</v>
+        <v/>
       </c>
       <c r="D11" t="str">
         <v>11506</v>
@@ -867,81 +867,81 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4768</v>
+        <v>材料*-KY</v>
       </c>
       <c r="B12" t="str">
-        <v>晶呈科技</v>
+        <v>材料*-KY</v>
       </c>
       <c r="C12" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D12" t="str">
         <v>11506</v>
       </c>
       <c r="E12" t="str">
-        <v>108,683</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>50,341</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>58,342</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>115.89</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>821,214</v>
+        <v/>
       </c>
       <c r="J12" t="str">
-        <v>340,615</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>480,599</v>
+        <v/>
       </c>
       <c r="L12" t="str">
-        <v>141.10</v>
+        <v/>
       </c>
       <c r="M12" t="str">
-        <v>本月營收較去年同期增加乃因客戶需求增加</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>5536</v>
+        <v>晶呈科技</v>
       </c>
       <c r="B13" t="str">
-        <v>聖暉*</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C13" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D13" t="str">
         <v>11506</v>
       </c>
       <c r="E13" t="str">
-        <v>4,774,283</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>3,822,387</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>951,896</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v>24.90</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>24,984,399</v>
+        <v/>
       </c>
       <c r="J13" t="str">
-        <v>19,463,905</v>
+        <v/>
       </c>
       <c r="K13" t="str">
-        <v>5,520,494</v>
+        <v/>
       </c>
       <c r="L13" t="str">
-        <v>28.36</v>
+        <v/>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -949,40 +949,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>5543</v>
+        <v>聖暉*</v>
       </c>
       <c r="B14" t="str">
-        <v>桓鼎-KY</v>
+        <v>聖暉*</v>
       </c>
       <c r="C14" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D14" t="str">
         <v>11506</v>
       </c>
       <c r="E14" t="str">
-        <v>239,202</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>236,163</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>3,039</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>1.29</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>1,640,805</v>
+        <v/>
       </c>
       <c r="J14" t="str">
-        <v>1,563,933</v>
+        <v/>
       </c>
       <c r="K14" t="str">
-        <v>76,872</v>
+        <v/>
       </c>
       <c r="L14" t="str">
-        <v>4.92</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,81 +990,81 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6613</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="B15" t="str">
-        <v>朋億*</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C15" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D15" t="str">
         <v>11506</v>
       </c>
       <c r="E15" t="str">
-        <v>1,992,776</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>903,950</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>1,088,826</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>120.45</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>6,128,443</v>
+        <v/>
       </c>
       <c r="J15" t="str">
-        <v>4,192,742</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>1,935,701</v>
+        <v/>
       </c>
       <c r="L15" t="str">
-        <v>46.17</v>
+        <v/>
       </c>
       <c r="M15" t="str">
-        <v>營收較去年同期增加主係因半導體擴廠暢旺</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>6977</v>
+        <v>朋億*</v>
       </c>
       <c r="B16" t="str">
-        <v>聯純</v>
+        <v>朋億*</v>
       </c>
       <c r="C16" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D16" t="str">
         <v>11506</v>
       </c>
       <c r="E16" t="str">
-        <v>132,460</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>199,441</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>-66,981</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v>-33.58</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v>757,951</v>
+        <v/>
       </c>
       <c r="J16" t="str">
-        <v>1,108,666</v>
+        <v/>
       </c>
       <c r="K16" t="str">
-        <v>-350,715</v>
+        <v/>
       </c>
       <c r="L16" t="str">
-        <v>-31.63</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1072,40 +1072,40 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>6938</v>
+        <v>聯純</v>
       </c>
       <c r="B17" t="str">
-        <v>藍新資訊</v>
+        <v>聯純</v>
       </c>
       <c r="C17" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D17" t="str">
         <v>11506</v>
       </c>
       <c r="E17" t="str">
-        <v>92,204</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>66,105</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>26,099</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>39.48</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v>329,471</v>
+        <v/>
       </c>
       <c r="J17" t="str">
-        <v>269,998</v>
+        <v/>
       </c>
       <c r="K17" t="str">
-        <v>59,473</v>
+        <v/>
       </c>
       <c r="L17" t="str">
-        <v>22.03</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,13 +1113,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2248</v>
+        <v>藍新資訊</v>
       </c>
       <c r="B18" t="str">
-        <v>華勝-KY</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C18" t="str">
-        <v>12</v>
+        <v/>
       </c>
       <c r="D18" t="str">
         <v>11506</v>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>7455</v>
+        <v>華勝-KY</v>
       </c>
       <c r="B19" t="str">
-        <v>樺緯物聯</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C19" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D19" t="str">
         <v>11506</v>
       </c>
       <c r="E19" t="str">
-        <v>54,816</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>100,925</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>-46,109</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>-45.69</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v>301,566</v>
+        <v/>
       </c>
       <c r="J19" t="str">
-        <v>443,699</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>-142,133</v>
+        <v/>
       </c>
       <c r="L19" t="str">
-        <v>-32.03</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,81 +1195,81 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>8045</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="B20" t="str">
-        <v>達運光電</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C20" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D20" t="str">
         <v>11506</v>
       </c>
       <c r="E20" t="str">
-        <v>118,547</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>111,477</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>7,070</v>
+        <v/>
       </c>
       <c r="H20" t="str">
-        <v>6.34</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v>920,958</v>
+        <v/>
       </c>
       <c r="J20" t="str">
-        <v>645,920</v>
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v>275,038</v>
+        <v/>
       </c>
       <c r="L20" t="str">
-        <v>42.58</v>
+        <v/>
       </c>
       <c r="M20" t="str">
-        <v>產品品項增換</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2429</v>
+        <v>達運光電</v>
       </c>
       <c r="B21" t="str">
-        <v>銘旺科</v>
+        <v>達運光電</v>
       </c>
       <c r="C21" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D21" t="str">
         <v>11506</v>
       </c>
       <c r="E21" t="str">
-        <v>21,247</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>28,185</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>-6,938</v>
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>-24.62</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v>200,442</v>
+        <v/>
       </c>
       <c r="J21" t="str">
-        <v>206,875</v>
+        <v/>
       </c>
       <c r="K21" t="str">
-        <v>-6,433</v>
+        <v/>
       </c>
       <c r="L21" t="str">
-        <v>-3.11</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1277,54 +1277,54 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>8096</v>
+        <v>銘旺科</v>
       </c>
       <c r="B22" t="str">
-        <v>擎亞</v>
+        <v>銘旺科</v>
       </c>
       <c r="C22" t="str">
-        <v>上櫃公司</v>
+        <v/>
       </c>
       <c r="D22" t="str">
         <v>11506</v>
       </c>
       <c r="E22" t="str">
-        <v>8,978,261</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>1,682,941</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>7,295,320</v>
+        <v/>
       </c>
       <c r="H22" t="str">
-        <v>433.49</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v>27,489,960</v>
+        <v/>
       </c>
       <c r="J22" t="str">
-        <v>21,364,408</v>
+        <v/>
       </c>
       <c r="K22" t="str">
-        <v>6,125,552</v>
+        <v/>
       </c>
       <c r="L22" t="str">
-        <v>28.67</v>
+        <v/>
       </c>
       <c r="M22" t="str">
-        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>7847</v>
+        <v>擎亞</v>
       </c>
       <c r="B23" t="str">
-        <v>豊漁</v>
+        <v>擎亞</v>
       </c>
       <c r="C23" t="str">
-        <v>16</v>
+        <v/>
       </c>
       <c r="D23" t="str">
         <v>11506</v>
@@ -1359,40 +1359,40 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>4441</v>
+        <v>豊漁</v>
       </c>
       <c r="B24" t="str">
-        <v>振大環球</v>
+        <v>豊漁</v>
       </c>
       <c r="C24" t="str">
-        <v>上市公司</v>
+        <v/>
       </c>
       <c r="D24" t="str">
         <v>11506</v>
       </c>
       <c r="E24" t="str">
-        <v>716,929</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>742,984</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>-26,055</v>
+        <v/>
       </c>
       <c r="H24" t="str">
-        <v>-3.51</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v>3,790,065</v>
+        <v/>
       </c>
       <c r="J24" t="str">
-        <v>3,425,552</v>
+        <v/>
       </c>
       <c r="K24" t="str">
-        <v>364,513</v>
+        <v/>
       </c>
       <c r="L24" t="str">
-        <v>10.64</v>
+        <v/>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>7854</v>
+        <v>振大環球</v>
       </c>
       <c r="B25" t="str">
-        <v>佐茂</v>
+        <v>振大環球</v>
       </c>
       <c r="C25" t="str">
-        <v>興櫃公司</v>
+        <v/>
       </c>
       <c r="D25" t="str">
         <v>11506</v>
       </c>
       <c r="E25" t="str">
-        <v>144,666</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>114,559</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>30,107</v>
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>26.28</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v>881,536</v>
+        <v/>
       </c>
       <c r="J25" t="str">
-        <v>829,142</v>
+        <v/>
       </c>
       <c r="K25" t="str">
-        <v>52,394</v>
+        <v/>
       </c>
       <c r="L25" t="str">
-        <v>6.32</v>
+        <v/>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,13 +1441,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2330</v>
+        <v>佐茂</v>
       </c>
       <c r="B26" t="str">
-        <v>台積電</v>
+        <v>佐茂</v>
       </c>
       <c r="C26" t="str">
-        <v>24</v>
+        <v/>
       </c>
       <c r="D26" t="str">
         <v>11506</v>
@@ -1482,13 +1482,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3135</v>
+        <v>2330</v>
       </c>
       <c r="B27" t="str">
-        <v>凌航</v>
+        <v>2330</v>
       </c>
       <c r="C27" t="str">
-        <v>24</v>
+        <v/>
       </c>
       <c r="D27" t="str">
         <v>11506</v>
@@ -1523,48 +1523,89 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
+        <v>3135</v>
+      </c>
+      <c r="B28" t="str">
+        <v>3135</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>11506</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
         <v>8112</v>
       </c>
-      <c r="B28" t="str">
-        <v>至上</v>
-      </c>
-      <c r="C28" t="str">
-        <v>上市公司</v>
-      </c>
-      <c r="D28" t="str">
-        <v>11506</v>
-      </c>
-      <c r="E28" t="str">
-        <v>61,628,573</v>
-      </c>
-      <c r="F28" t="str">
-        <v>18,609,520</v>
-      </c>
-      <c r="G28" t="str">
-        <v>43,019,053</v>
-      </c>
-      <c r="H28" t="str">
-        <v>231.17</v>
-      </c>
-      <c r="I28" t="str">
-        <v>260,775,359</v>
-      </c>
-      <c r="J28" t="str">
-        <v>102,675,279</v>
-      </c>
-      <c r="K28" t="str">
-        <v>158,100,080</v>
-      </c>
-      <c r="L28" t="str">
-        <v>153.98</v>
-      </c>
-      <c r="M28" t="str">
-        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
+      <c r="B29" t="str">
+        <v>8112</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>11506</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/monthly-revenue-11506.xlsx
+++ b/public/data/monthly-revenue-11506.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M28"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -457,40 +457,40 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>友威科</v>
+        <v>3580</v>
       </c>
       <c r="B2" t="str">
         <v>友威科</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D2" t="str">
         <v>11506</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>43,243</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>44,502</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>-1,259</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>-2.83</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>189,510</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>203,939</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>-14,429</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>-7.08</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -498,40 +498,40 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>德微</v>
+        <v>3675</v>
       </c>
       <c r="B3" t="str">
         <v>德微</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D3" t="str">
         <v>11506</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>279,963</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>215,370</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>64,593</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>29.99</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>1,485,502</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>1,268,444</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>217,058</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>17.11</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -539,163 +539,163 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>樺漢</v>
+        <v>6414</v>
       </c>
       <c r="B4" t="str">
         <v>樺漢</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D4" t="str">
         <v>11506</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>17,661,254</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>11,251,646</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>6,409,608</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>56.97</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>85,293,283</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>69,158,805</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>16,134,478</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>23.33</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>AI需求增加、客戶需求強勁</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>瑞祺電通</v>
+        <v>6416</v>
       </c>
       <c r="B5" t="str">
         <v>瑞祺電通</v>
       </c>
       <c r="C5" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D5" t="str">
         <v>11506</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>667,868</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>421,055</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>246,813</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>58.62</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>2,390,895</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>2,170,447</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>220,448</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>10.16</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>因應上半年部分區域訂單物料遞延，公司於階段性齊料後迅速優化生產排程並加速出貨，帶動6月單月營收成長。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>昇貿</v>
+        <v>3305</v>
       </c>
       <c r="B6" t="str">
         <v>昇貿</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D6" t="str">
         <v>11506</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>1,445,505</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>821,303</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>624,202</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>76.00</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>7,984,628</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>4,851,602</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>3,133,026</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>64.58</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>銷售量增加及原料價格上漲</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>慶康科技</v>
+        <v>8098</v>
       </c>
       <c r="B7" t="str">
         <v>慶康科技</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D7" t="str">
         <v>11506</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>79,912</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>61,161</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>18,751</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>30.66</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>362,103</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>323,896</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>38,207</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>11.80</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -703,81 +703,81 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>世紀鋼</v>
+        <v>9958</v>
       </c>
       <c r="B8" t="str">
         <v>世紀鋼</v>
       </c>
       <c r="C8" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D8" t="str">
         <v>11506</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>2,138,665</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>1,303,359</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>835,306</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>64.09</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>10,181,252</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>7,881,335</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>2,299,917</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>29.18</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>本月增加百分比達50%以上，主要係風力事業案依進度如期交貨及相關工程收入挹注所致。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>騰輝電子-KY</v>
+        <v>6672</v>
       </c>
       <c r="B9" t="str">
         <v>騰輝電子-KY</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D9" t="str">
         <v>11506</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>573,491</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>341,113</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>232,378</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>68.12</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>2,859,714</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>2,125,423</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>734,291</v>
       </c>
       <c r="L9" t="str">
-        <v/>
+        <v>34.55</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -785,40 +785,40 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>中砂</v>
+        <v>1560</v>
       </c>
       <c r="B10" t="str">
         <v>中砂</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D10" t="str">
         <v>11506</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>832,959</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>715,653</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>117,306</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>16.39</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>4,785,855</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>3,890,219</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>895,636</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>23.02</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -826,13 +826,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>耀登</v>
+        <v>3138</v>
       </c>
       <c r="B11" t="str">
         <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>27</v>
       </c>
       <c r="D11" t="str">
         <v>11506</v>
@@ -867,81 +867,81 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>材料*-KY</v>
+        <v>4768</v>
       </c>
       <c r="B12" t="str">
-        <v>材料*-KY</v>
+        <v>晶呈科技</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D12" t="str">
         <v>11506</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>108,683</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>50,341</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>58,342</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>115.89</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>821,214</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>340,615</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>480,599</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>141.10</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>本月營收較去年同期增加乃因客戶需求增加</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>晶呈科技</v>
+        <v>5536</v>
       </c>
       <c r="B13" t="str">
-        <v>晶呈科技</v>
+        <v>聖暉*</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D13" t="str">
         <v>11506</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>4,774,283</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>3,822,387</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>951,896</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>24.90</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>24,984,399</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>19,463,905</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>5,520,494</v>
       </c>
       <c r="L13" t="str">
-        <v/>
+        <v>28.36</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -949,40 +949,40 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>聖暉*</v>
+        <v>5543</v>
       </c>
       <c r="B14" t="str">
-        <v>聖暉*</v>
+        <v>桓鼎-KY</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D14" t="str">
         <v>11506</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>239,202</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>236,163</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>3,039</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>1.29</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>1,640,805</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>1,563,933</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>76,872</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>4.92</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -990,81 +990,81 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>桓鼎-KY</v>
+        <v>6613</v>
       </c>
       <c r="B15" t="str">
-        <v>桓鼎-KY</v>
+        <v>朋億*</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D15" t="str">
         <v>11506</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>1,992,776</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>903,950</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>1,088,826</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>120.45</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>6,128,443</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>4,192,742</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>1,935,701</v>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>46.17</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>營收較去年同期增加主係因半導體擴廠暢旺</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>朋億*</v>
+        <v>6977</v>
       </c>
       <c r="B16" t="str">
-        <v>朋億*</v>
+        <v>聯純</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D16" t="str">
         <v>11506</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>132,460</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>199,441</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>-66,981</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>-33.58</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>757,951</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>1,108,666</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>-350,715</v>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>-31.63</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1072,40 +1072,40 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>聯純</v>
+        <v>6938</v>
       </c>
       <c r="B17" t="str">
-        <v>聯純</v>
+        <v>藍新資訊</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D17" t="str">
         <v>11506</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>92,204</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>66,105</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>26,099</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>39.48</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>329,471</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>269,998</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>59,473</v>
       </c>
       <c r="L17" t="str">
-        <v/>
+        <v>22.03</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1113,13 +1113,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>藍新資訊</v>
+        <v>2248</v>
       </c>
       <c r="B18" t="str">
-        <v>藍新資訊</v>
+        <v>華勝-KY</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>12</v>
       </c>
       <c r="D18" t="str">
         <v>11506</v>
@@ -1154,40 +1154,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>華勝-KY</v>
+        <v>7455</v>
       </c>
       <c r="B19" t="str">
-        <v>華勝-KY</v>
+        <v>樺緯物聯</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D19" t="str">
         <v>11506</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>54,816</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>100,925</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>-46,109</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>-45.69</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>301,566</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>443,699</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>-142,133</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>-32.03</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1195,81 +1195,81 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>樺緯物聯</v>
+        <v>8045</v>
       </c>
       <c r="B20" t="str">
-        <v>樺緯物聯</v>
+        <v>達運光電</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D20" t="str">
         <v>11506</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>118,547</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>111,477</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>7,070</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>6.34</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>920,958</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>645,920</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>275,038</v>
       </c>
       <c r="L20" t="str">
-        <v/>
+        <v>42.58</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>產品品項增換</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>達運光電</v>
+        <v>2429</v>
       </c>
       <c r="B21" t="str">
-        <v>達運光電</v>
+        <v>銘旺科</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D21" t="str">
         <v>11506</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>21,247</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>28,185</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>-6,938</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>-24.62</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>200,442</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>206,875</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>-6,433</v>
       </c>
       <c r="L21" t="str">
-        <v/>
+        <v>-3.11</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1277,54 +1277,54 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>銘旺科</v>
+        <v>8096</v>
       </c>
       <c r="B22" t="str">
-        <v>銘旺科</v>
+        <v>擎亞</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>上櫃公司</v>
       </c>
       <c r="D22" t="str">
         <v>11506</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>8,978,261</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>1,682,941</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>7,295,320</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>433.49</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>27,489,960</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>21,364,408</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>6,125,552</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>28.67</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>因伺服器記憶體出貨量增加，致使營收較去年同期成長</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>擎亞</v>
+        <v>7847</v>
       </c>
       <c r="B23" t="str">
-        <v>擎亞</v>
+        <v>豊漁</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>16</v>
       </c>
       <c r="D23" t="str">
         <v>11506</v>
@@ -1359,40 +1359,40 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>豊漁</v>
+        <v>4441</v>
       </c>
       <c r="B24" t="str">
-        <v>豊漁</v>
+        <v>振大環球</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D24" t="str">
         <v>11506</v>
       </c>
       <c r="E24" t="str">
-        <v/>
+        <v>716,929</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>742,984</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>-26,055</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>-3.51</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>3,790,065</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>3,425,552</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>364,513</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>10.64</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -1400,40 +1400,40 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>振大環球</v>
+        <v>7854</v>
       </c>
       <c r="B25" t="str">
-        <v>振大環球</v>
+        <v>佐茂</v>
       </c>
       <c r="C25" t="str">
-        <v/>
+        <v>興櫃公司</v>
       </c>
       <c r="D25" t="str">
         <v>11506</v>
       </c>
       <c r="E25" t="str">
-        <v/>
+        <v>144,666</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>114,559</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>30,107</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>26.28</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>881,536</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>829,142</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>52,394</v>
       </c>
       <c r="L25" t="str">
-        <v/>
+        <v>6.32</v>
       </c>
       <c r="M25" t="str">
         <v/>
@@ -1441,13 +1441,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>佐茂</v>
+        <v>2330</v>
       </c>
       <c r="B26" t="str">
-        <v>佐茂</v>
+        <v>台積電</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>24</v>
       </c>
       <c r="D26" t="str">
         <v>11506</v>
@@ -1482,13 +1482,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2330</v>
+        <v>3135</v>
       </c>
       <c r="B27" t="str">
-        <v>2330</v>
+        <v>凌航</v>
       </c>
       <c r="C27" t="str">
-        <v/>
+        <v>24</v>
       </c>
       <c r="D27" t="str">
         <v>11506</v>
@@ -1523,89 +1523,48 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>3135</v>
+        <v>8112</v>
       </c>
       <c r="B28" t="str">
-        <v>3135</v>
+        <v>至上</v>
       </c>
       <c r="C28" t="str">
-        <v/>
+        <v>上市公司</v>
       </c>
       <c r="D28" t="str">
         <v>11506</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>61,628,573</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>18,609,520</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>43,019,053</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>231.17</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>260,775,359</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>102,675,279</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>158,100,080</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>153.98</v>
       </c>
       <c r="M28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>8112</v>
-      </c>
-      <c r="B29" t="str">
-        <v>8112</v>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <v>11506</v>
-      </c>
-      <c r="E29" t="str">
-        <v/>
-      </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
-      <c r="M29" t="str">
-        <v/>
+        <v>營收大幅成長，主要係記憶體等零組件價格持續上漲，伺服器及手機客戶拉貨動能強勁所致。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/monthly-revenue-11506.xlsx
+++ b/public/data/monthly-revenue-11506.xlsx
@@ -832,34 +832,34 @@
         <v>耀登</v>
       </c>
       <c r="C11" t="str">
-        <v>27</v>
+        <v>上市公司</v>
       </c>
       <c r="D11" t="str">
         <v>11506</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>141,121</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>143,190</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>-2,069</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>-1.44</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>844,886</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>742,037</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>102,849</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>13.86</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -1119,34 +1119,34 @@
         <v>華勝-KY</v>
       </c>
       <c r="C18" t="str">
-        <v>12</v>
+        <v>上市公司</v>
       </c>
       <c r="D18" t="str">
         <v>11506</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>307,728</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>148,957</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>158,771</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>106.59</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>1,332,132</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>900,780</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>431,352</v>
       </c>
       <c r="L18" t="str">
-        <v/>
+        <v>47.89</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1324,34 +1324,34 @@
         <v>豊漁</v>
       </c>
       <c r="C23" t="str">
-        <v>16</v>
+        <v>興櫃公司</v>
       </c>
       <c r="D23" t="str">
         <v>11506</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>96,303</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>73,691</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>22,612</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>30.68</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>582,845</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>489,201</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>93,644</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>19.14</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1447,37 +1447,37 @@
         <v>台積電</v>
       </c>
       <c r="C26" t="str">
-        <v>24</v>
+        <v>上市公司</v>
       </c>
       <c r="D26" t="str">
         <v>11506</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>442,679,969</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>263,708,978</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>178,970,991</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>67.87</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>2,404,483,690</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>1,773,045,533</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>631,438,157</v>
       </c>
       <c r="L26" t="str">
-        <v/>
+        <v>35.61</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>因先進製程產品需求增加所致。</v>
       </c>
     </row>
     <row r="27">
@@ -1488,37 +1488,37 @@
         <v>凌航</v>
       </c>
       <c r="C27" t="str">
-        <v>24</v>
+        <v>上市公司</v>
       </c>
       <c r="D27" t="str">
         <v>11506</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>1,610,089</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>643,976</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>966,113</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>150.02</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>11,262,486</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>3,162,779</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>8,099,707</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>256.09</v>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>市場價格上漲及需求增加。</v>
       </c>
     </row>
     <row r="28">
